--- a/Orders_import.xlsx
+++ b/Orders_import.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -52,10 +51,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -470,7 +470,7 @@
       <c r="A2" t="n">
         <v>1001</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <v>46289</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -502,7 +502,7 @@
       <c r="A3" t="n">
         <v>1001</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="3" t="n">
         <v>46289</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -534,7 +534,7 @@
       <c r="A4" t="n">
         <v>1001</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <v>46289</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -566,7 +566,7 @@
       <c r="A5" t="n">
         <v>1002</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <v>46282</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -598,7 +598,7 @@
       <c r="A6" t="n">
         <v>1002</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>46282</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -630,7 +630,7 @@
       <c r="A7" t="n">
         <v>1002</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="3" t="n">
         <v>46282</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -662,7 +662,7 @@
       <c r="A8" t="n">
         <v>1003</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <v>46277</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -694,7 +694,7 @@
       <c r="A9" t="n">
         <v>1003</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="3" t="n">
         <v>46277</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -726,7 +726,7 @@
       <c r="A10" t="n">
         <v>1003</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="3" t="n">
         <v>46277</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -758,7 +758,7 @@
       <c r="A11" t="n">
         <v>1003</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="3" t="n">
         <v>46277</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -790,7 +790,7 @@
       <c r="A12" t="n">
         <v>1004</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="3" t="n">
         <v>46273</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -822,7 +822,7 @@
       <c r="A13" t="n">
         <v>1004</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="3" t="n">
         <v>46273</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -854,7 +854,7 @@
       <c r="A14" t="n">
         <v>1005</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="3" t="n">
         <v>46268</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -886,7 +886,7 @@
       <c r="A15" t="n">
         <v>1005</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="3" t="n">
         <v>46268</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -918,7 +918,7 @@
       <c r="A16" t="n">
         <v>1005</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="3" t="n">
         <v>46268</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -950,7 +950,7 @@
       <c r="A17" t="n">
         <v>1006</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" s="3" t="n">
         <v>46223</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -982,7 +982,7 @@
       <c r="A18" t="n">
         <v>1006</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="3" t="n">
         <v>46223</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="A19" t="n">
         <v>1006</v>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" s="3" t="n">
         <v>46223</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -1046,7 +1046,7 @@
       <c r="A20" t="n">
         <v>1007</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="3" t="n">
         <v>46217</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -1078,7 +1078,7 @@
       <c r="A21" t="n">
         <v>1007</v>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" s="3" t="n">
         <v>46217</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -1110,7 +1110,7 @@
       <c r="A22" t="n">
         <v>1007</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" s="3" t="n">
         <v>46217</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -1142,7 +1142,7 @@
       <c r="A23" t="n">
         <v>1008</v>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" s="3" t="n">
         <v>46208</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -1174,7 +1174,7 @@
       <c r="A24" t="n">
         <v>1008</v>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" s="3" t="n">
         <v>46208</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1206,7 +1206,7 @@
       <c r="A25" t="n">
         <v>1008</v>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B25" s="3" t="n">
         <v>46208</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -1238,7 +1238,7 @@
       <c r="A26" t="n">
         <v>1009</v>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B26" s="3" t="n">
         <v>46195</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="A27" t="n">
         <v>1009</v>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B27" s="3" t="n">
         <v>46195</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -1302,7 +1302,7 @@
       <c r="A28" t="n">
         <v>1009</v>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" s="3" t="n">
         <v>46195</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -1334,7 +1334,7 @@
       <c r="A29" t="n">
         <v>1010</v>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B29" s="3" t="n">
         <v>46182</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -1366,7 +1366,7 @@
       <c r="A30" t="n">
         <v>1010</v>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B30" s="3" t="n">
         <v>46182</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -1398,7 +1398,7 @@
       <c r="A31" t="n">
         <v>1010</v>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B31" s="3" t="n">
         <v>46182</v>
       </c>
       <c r="C31" t="inlineStr">
